--- a/docs/files/exports/combined-combined-pricing-parameters.xlsx
+++ b/docs/files/exports/combined-combined-pricing-parameters.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Combined Web + App Pricing Parameters</t>
+          <t>Pricing Parameters Reference</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4,221 words</t>
+          <t>4,230 words</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Combined Web + App Pricing Parameters Unified pricing parameters reference covering all line items, cost factors, and configurable variables for both website and mobile application engagements. Scope: This document cover...</t>
+          <t>Pricing Parameters Reference Unified pricing parameters sheet covering all cost line items, complexity multipliers, and estimation formulas for both Website and Mobile Application engagements. Covers: 🌐 Website / Web App...</t>
         </is>
       </c>
     </row>
